--- a/resources/data-imports/Monsters/weekly-monsters-purgatory.xlsx
+++ b/resources/data-imports/Monsters/weekly-monsters-purgatory.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -411,34 +411,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -845,7 +845,7 @@
         <v>0.015955343603399</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>1008242009.45287</v>
+        <v>15000000</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>0.0201539066179668</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1169005492.09072</v>
+        <v>18338600</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>0.0254572989502525</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1355402599.50074</v>
+        <v>22420282</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0.0321562505040478</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1571520595.20931</v>
+        <v>27410439</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0.0406179951965728</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1822098454.05102</v>
+        <v>33511271</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         <v>0.0513064025789055</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>2112630777.08054</v>
+        <v>40969986</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>0</v>
@@ -1598,7 +1598,7 @@
         <v>0.0648074069842528</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>2449488275.64449</v>
+        <v>50088811</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>0.0818611282200753</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>2840057466.55421</v>
+        <v>61237243</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>0.103402444647907</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>3292902641.55605</v>
+        <v>74867019</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>0</v>
@@ -1976,7 +1976,7 @@
         <v>0.13061224285132</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>3817953662.72031</v>
+        <v>91530420</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>0</v>
@@ -2101,7 +2101,7 @@
         <v>0.164982153378881</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>4426723701.6735</v>
+        <v>111902648</v>
       </c>
       <c r="X12" s="1" t="n">
         <v>0</v>
@@ -2229,7 +2229,7 @@
         <v>0.208396321350341</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>5132561697.19875</v>
+        <v>136809191</v>
       </c>
       <c r="X13" s="1" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
         <v>0.263234694558872</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>5950945067.0239</v>
+        <v>167259265</v>
       </c>
       <c r="X14" s="1" t="n">
         <v>0</v>
@@ -2479,7 +2479,7 @@
         <v>0.332503491282904</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>6899819092.29932</v>
+        <v>204486714</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         <v>0.420000000002258</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>7999990416.69308</v>
+        <v>249999998</v>
       </c>
       <c r="X16" s="1" t="n">
         <v>0</v>
